--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87373</v>
+        <v>87375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87324</v>
+        <v>87326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87324</v>
+        <v>87326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87375</v>
+        <v>87377</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87326</v>
+        <v>87328</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87326</v>
+        <v>87328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91630</v>
+        <v>91632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87377</v>
+        <v>87378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87378</v>
+        <v>87384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87384</v>
+        <v>87388</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87388</v>
+        <v>87390</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87390</v>
+        <v>87403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91645</v>
+        <v>91658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87403</v>
+        <v>87405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87405</v>
+        <v>87408</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87408</v>
+        <v>87418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91663</v>
+        <v>91673</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87418</v>
+        <v>87419</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91673</v>
+        <v>91674</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87419</v>
+        <v>87422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91674</v>
+        <v>91677</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91677</v>
+        <v>91679</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87422</v>
+        <v>87427</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91679</v>
+        <v>91684</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87427</v>
+        <v>87438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91684</v>
+        <v>91696</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87438</v>
+        <v>87439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91696</v>
+        <v>91697</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 357-2025 artfynd.xlsx
+++ b/artfynd/A 357-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136923615</v>
       </c>
       <c r="B7" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136923616</v>
       </c>
       <c r="B8" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>136923617</v>
       </c>
       <c r="B9" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136923618</v>
       </c>
       <c r="B10" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136923619</v>
       </c>
       <c r="B11" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136923608</v>
       </c>
       <c r="B12" t="n">
-        <v>87439</v>
+        <v>87442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>136923612</v>
       </c>
       <c r="B49" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>136923613</v>
       </c>
       <c r="B50" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136923614</v>
       </c>
       <c r="B51" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>136923610</v>
       </c>
       <c r="B53" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136923606</v>
       </c>
       <c r="B55" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136923620</v>
       </c>
       <c r="B56" t="n">
-        <v>91697</v>
+        <v>91700</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136923622</v>
       </c>
       <c r="B57" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136923623</v>
       </c>
       <c r="B58" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136923624</v>
       </c>
       <c r="B59" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>136923626</v>
       </c>
       <c r="B60" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>136923627</v>
       </c>
       <c r="B61" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>136923628</v>
       </c>
       <c r="B62" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>136923629</v>
       </c>
       <c r="B63" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>136923630</v>
       </c>
       <c r="B64" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136923631</v>
       </c>
       <c r="B65" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>136923632</v>
       </c>
       <c r="B66" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>136923633</v>
       </c>
       <c r="B67" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136923634</v>
       </c>
       <c r="B68" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>136923635</v>
       </c>
       <c r="B69" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136923621</v>
       </c>
       <c r="B77" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
